--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI15"/>
+  <dimension ref="A1:BI16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3367,6 +3367,195 @@
         <v>16728</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20260806</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4455.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4259.75</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4019.85</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>24</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>24</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4252.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4455.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4453.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4254.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4452.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4455.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4234.9</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>4455.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4263.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4030.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4263.69</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1677001</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1678</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>16772</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI16"/>
+  <dimension ref="A1:BI17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3556,6 +3556,195 @@
         <v>16772</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4261.18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4022.14</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4267.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4258.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4457.9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4235.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4263.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4033.89</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4265.46</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1680231</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1682</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>16804</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI17"/>
+  <dimension ref="A1:BI18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3745,6 +3745,195 @@
         <v>16804</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20260808</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4261.79</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4022.7</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>24</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4259.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4281.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4457.9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4375.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>4235.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>4459.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4350.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4263.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4037.45</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4266.63</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1681677</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1682</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>16817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI18"/>
+  <dimension ref="A1:BI19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -4550,6 +4550,195 @@
         <v>16852</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20260809</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4263.97</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4025.87</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>24</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>24</v>
+      </c>
+      <c r="O19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4261.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4281.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4459.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4375.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4235.2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4267.1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4038.98</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4267.79</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1689551</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1690</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>16898</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI19"/>
+  <dimension ref="A1:BI20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -4739,6 +4739,195 @@
         <v>16898</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20260810</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4265.58</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4027.49</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>24</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4261.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4375.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>4235.2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4040.33</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4268.79</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1695069</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1696</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>16951</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI20"/>
+  <dimension ref="A1:BI21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -4928,6 +4928,195 @@
         <v>16951</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20260811</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4266.81</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4029.24</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" t="n">
+        <v>25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>24</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4261.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4375.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>4253</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4361.1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4041.22</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4269.68</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1699938</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1700</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>17001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI21"/>
+  <dimension ref="A1:BI22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -5117,6 +5117,195 @@
         <v>17001</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20260812</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4267.79</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4031.63</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>24</v>
+      </c>
+      <c r="L22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4285.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4361.1</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4041.9</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>4270.56</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1704481</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1706</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>17045</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI22"/>
+  <dimension ref="A1:BI23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -5306,6 +5306,195 @@
         <v>17045</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20260813</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4035.53</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>24</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>24</v>
+      </c>
+      <c r="O23" t="n">
+        <v>25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4042.71</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4271.25</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1707787</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>17078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI23"/>
+  <dimension ref="A1:BI24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -5495,6 +5495,195 @@
         <v>17078</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20260814</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4268.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4035.83</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" t="n">
+        <v>25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>24</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4042.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4271.28</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1707945</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>17080</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI24"/>
+  <dimension ref="A1:BI25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -5684,6 +5684,195 @@
         <v>17080</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20260815</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>21</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4268.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Speedk-T血DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" t="n">
+        <v>24</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>24</v>
+      </c>
+      <c r="O25" t="n">
+        <v>25</v>
+      </c>
+      <c r="P25" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4042.85</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4271.29</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1707924</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>17082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -5873,6 +5873,195 @@
         <v>17082</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20260816</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>21</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4268.27</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4036.1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>24</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4042.86</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4271.29</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1707876</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI26"/>
+  <dimension ref="A1:BI27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -6062,6 +6062,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20260817</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4268.27</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4036.08</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>24</v>
+      </c>
+      <c r="J27" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>24</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4042.86</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4271.29</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1707838</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>17080</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI27"/>
+  <dimension ref="A1:BI28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -6251,6 +6251,195 @@
         <v>17080</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20260818</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4036.03</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J28" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>24</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25</v>
+      </c>
+      <c r="N28" t="n">
+        <v>24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4042.84</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>4271.28</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1707804</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI28"/>
+  <dimension ref="A1:BI29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -6440,6 +6440,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>20260819</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25</v>
+      </c>
+      <c r="K29" t="n">
+        <v>24</v>
+      </c>
+      <c r="L29" t="n">
+        <v>25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>24</v>
+      </c>
+      <c r="O29" t="n">
+        <v>25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4042.84</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4271.28</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI29"/>
+  <dimension ref="A1:BI30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -6629,6 +6629,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>20260820</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" t="n">
+        <v>25</v>
+      </c>
+      <c r="K30" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" t="n">
+        <v>25</v>
+      </c>
+      <c r="M30" t="n">
+        <v>25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>24</v>
+      </c>
+      <c r="O30" t="n">
+        <v>25</v>
+      </c>
+      <c r="P30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4042.81</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>4271.28</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI30"/>
+  <dimension ref="A1:BI31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -6818,6 +6818,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>20260821</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-T复仇,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>24</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>24</v>
+      </c>
+      <c r="O31" t="n">
+        <v>25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>4042.76</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4271.28</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI31"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7007,6 +7007,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>20260822</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>22</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>24</v>
+      </c>
+      <c r="J32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>24</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25</v>
+      </c>
+      <c r="M32" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>24</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25</v>
+      </c>
+      <c r="P32" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4042.74</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4271.25</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7196,6 +7196,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>20260823</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>22</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>24</v>
+      </c>
+      <c r="J33" t="n">
+        <v>25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>24</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>24</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4042.73</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4271.25</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI33"/>
+  <dimension ref="A1:BI34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7385,6 +7385,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>20260824</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>22</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>24</v>
+      </c>
+      <c r="J34" t="n">
+        <v>25</v>
+      </c>
+      <c r="K34" t="n">
+        <v>24</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25</v>
+      </c>
+      <c r="M34" t="n">
+        <v>25</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25</v>
+      </c>
+      <c r="P34" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4042.71</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4271.25</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI34"/>
+  <dimension ref="A1:BI35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7574,6 +7574,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>20260825</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>22</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>24</v>
+      </c>
+      <c r="J35" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>24</v>
+      </c>
+      <c r="L35" t="n">
+        <v>25</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>24</v>
+      </c>
+      <c r="O35" t="n">
+        <v>25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>4042.69</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>4271.2</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI35"/>
+  <dimension ref="A1:BI36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7763,6 +7763,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20260826</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D噬灭,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25</v>
+      </c>
+      <c r="K36" t="n">
+        <v>24</v>
+      </c>
+      <c r="L36" t="n">
+        <v>25</v>
+      </c>
+      <c r="M36" t="n">
+        <v>25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>24</v>
+      </c>
+      <c r="O36" t="n">
+        <v>25</v>
+      </c>
+      <c r="P36" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>4042.69</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>4271.16</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI36"/>
+  <dimension ref="A1:BI37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -7952,6 +7952,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20260827</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>24</v>
+      </c>
+      <c r="J37" t="n">
+        <v>25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>24</v>
+      </c>
+      <c r="L37" t="n">
+        <v>25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>25</v>
+      </c>
+      <c r="N37" t="n">
+        <v>24</v>
+      </c>
+      <c r="O37" t="n">
+        <v>25</v>
+      </c>
+      <c r="P37" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4042.67</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4271.16</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI37"/>
+  <dimension ref="A1:BI38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -8141,6 +8141,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>23</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>24</v>
+      </c>
+      <c r="J38" t="n">
+        <v>25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>24</v>
+      </c>
+      <c r="L38" t="n">
+        <v>25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>25</v>
+      </c>
+      <c r="N38" t="n">
+        <v>24</v>
+      </c>
+      <c r="O38" t="n">
+        <v>25</v>
+      </c>
+      <c r="P38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>4042.65</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI38"/>
+  <dimension ref="A1:BI39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -8330,6 +8330,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>20260829</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>23</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>24</v>
+      </c>
+      <c r="J39" t="n">
+        <v>25</v>
+      </c>
+      <c r="K39" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" t="n">
+        <v>25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>24</v>
+      </c>
+      <c r="O39" t="n">
+        <v>25</v>
+      </c>
+      <c r="P39" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4042.65</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI39"/>
+  <dimension ref="A1:BI40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -8519,6 +8519,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20260830</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>23</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" t="n">
+        <v>24</v>
+      </c>
+      <c r="L40" t="n">
+        <v>25</v>
+      </c>
+      <c r="M40" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>24</v>
+      </c>
+      <c r="O40" t="n">
+        <v>25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>4042.62</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -8708,6 +8708,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20260831</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>23</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>24</v>
+      </c>
+      <c r="J41" t="n">
+        <v>25</v>
+      </c>
+      <c r="K41" t="n">
+        <v>24</v>
+      </c>
+      <c r="L41" t="n">
+        <v>25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" t="n">
+        <v>24</v>
+      </c>
+      <c r="O41" t="n">
+        <v>25</v>
+      </c>
+      <c r="P41" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>4042.61</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI41"/>
+  <dimension ref="A1:BI42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -8897,6 +8897,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>20260901</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>23</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>24</v>
+      </c>
+      <c r="J42" t="n">
+        <v>25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>24</v>
+      </c>
+      <c r="L42" t="n">
+        <v>25</v>
+      </c>
+      <c r="M42" t="n">
+        <v>25</v>
+      </c>
+      <c r="N42" t="n">
+        <v>24</v>
+      </c>
+      <c r="O42" t="n">
+        <v>25</v>
+      </c>
+      <c r="P42" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4042.6</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI42"/>
+  <dimension ref="A1:BI43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -9086,6 +9086,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>20260902</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="n">
+        <v>25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>24</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25</v>
+      </c>
+      <c r="N43" t="n">
+        <v>24</v>
+      </c>
+      <c r="O43" t="n">
+        <v>25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V43" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>4042.6</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI43"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -9275,6 +9275,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>20260903</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>24</v>
+      </c>
+      <c r="L44" t="n">
+        <v>25</v>
+      </c>
+      <c r="M44" t="n">
+        <v>25</v>
+      </c>
+      <c r="N44" t="n">
+        <v>24</v>
+      </c>
+      <c r="O44" t="n">
+        <v>25</v>
+      </c>
+      <c r="P44" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V44" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>4042.59</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI44"/>
+  <dimension ref="A1:BI45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -9464,6 +9464,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>24</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" t="n">
+        <v>25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>24</v>
+      </c>
+      <c r="L45" t="n">
+        <v>25</v>
+      </c>
+      <c r="M45" t="n">
+        <v>25</v>
+      </c>
+      <c r="N45" t="n">
+        <v>24</v>
+      </c>
+      <c r="O45" t="n">
+        <v>25</v>
+      </c>
+      <c r="P45" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>4042.58</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>4271.1</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI45"/>
+  <dimension ref="A1:BI46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -9653,6 +9653,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>20260905</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>24</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>24</v>
+      </c>
+      <c r="J46" t="n">
+        <v>25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>24</v>
+      </c>
+      <c r="L46" t="n">
+        <v>25</v>
+      </c>
+      <c r="M46" t="n">
+        <v>25</v>
+      </c>
+      <c r="N46" t="n">
+        <v>24</v>
+      </c>
+      <c r="O46" t="n">
+        <v>25</v>
+      </c>
+      <c r="P46" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>4042.57</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>4271.07</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI46"/>
+  <dimension ref="A1:BI47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -9842,6 +9842,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>20260906</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>24</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>24</v>
+      </c>
+      <c r="J47" t="n">
+        <v>25</v>
+      </c>
+      <c r="K47" t="n">
+        <v>24</v>
+      </c>
+      <c r="L47" t="n">
+        <v>25</v>
+      </c>
+      <c r="M47" t="n">
+        <v>25</v>
+      </c>
+      <c r="N47" t="n">
+        <v>24</v>
+      </c>
+      <c r="O47" t="n">
+        <v>25</v>
+      </c>
+      <c r="P47" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>4042.56</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>4271.07</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI47"/>
+  <dimension ref="A1:BI48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10031,6 +10031,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>20260907</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-D踏风,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>24</v>
+      </c>
+      <c r="J48" t="n">
+        <v>25</v>
+      </c>
+      <c r="K48" t="n">
+        <v>24</v>
+      </c>
+      <c r="L48" t="n">
+        <v>25</v>
+      </c>
+      <c r="M48" t="n">
+        <v>25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>24</v>
+      </c>
+      <c r="O48" t="n">
+        <v>25</v>
+      </c>
+      <c r="P48" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>4042.54</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>4271.07</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI48"/>
+  <dimension ref="A1:BI49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10220,6 +10220,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>20260908</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>24</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-D踏风,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>24</v>
+      </c>
+      <c r="J49" t="n">
+        <v>25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>24</v>
+      </c>
+      <c r="L49" t="n">
+        <v>25</v>
+      </c>
+      <c r="M49" t="n">
+        <v>25</v>
+      </c>
+      <c r="N49" t="n">
+        <v>24</v>
+      </c>
+      <c r="O49" t="n">
+        <v>25</v>
+      </c>
+      <c r="P49" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>4042.54</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>4271.07</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI49"/>
+  <dimension ref="A1:BI50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10409,6 +10409,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>20260909</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-D踏风,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>24</v>
+      </c>
+      <c r="J50" t="n">
+        <v>25</v>
+      </c>
+      <c r="K50" t="n">
+        <v>24</v>
+      </c>
+      <c r="L50" t="n">
+        <v>25</v>
+      </c>
+      <c r="M50" t="n">
+        <v>25</v>
+      </c>
+      <c r="N50" t="n">
+        <v>24</v>
+      </c>
+      <c r="O50" t="n">
+        <v>25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W50" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X50" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>4042.53</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>4271.07</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI50"/>
+  <dimension ref="A1:BI51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10598,6 +10598,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>20260910</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-D踏风,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>24</v>
+      </c>
+      <c r="J51" t="n">
+        <v>25</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24</v>
+      </c>
+      <c r="L51" t="n">
+        <v>25</v>
+      </c>
+      <c r="M51" t="n">
+        <v>25</v>
+      </c>
+      <c r="N51" t="n">
+        <v>24</v>
+      </c>
+      <c r="O51" t="n">
+        <v>25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V51" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W51" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>4042.51</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>4271.06</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI51"/>
+  <dimension ref="A1:BI52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10787,6 +10787,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" t="n">
+        <v>25</v>
+      </c>
+      <c r="K52" t="n">
+        <v>24</v>
+      </c>
+      <c r="L52" t="n">
+        <v>25</v>
+      </c>
+      <c r="M52" t="n">
+        <v>25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>24</v>
+      </c>
+      <c r="O52" t="n">
+        <v>25</v>
+      </c>
+      <c r="P52" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>4042.47</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>4271.06</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI52"/>
+  <dimension ref="A1:BI53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -10976,6 +10976,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>20260912</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>25</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>24</v>
+      </c>
+      <c r="J53" t="n">
+        <v>25</v>
+      </c>
+      <c r="K53" t="n">
+        <v>24</v>
+      </c>
+      <c r="L53" t="n">
+        <v>25</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>24</v>
+      </c>
+      <c r="O53" t="n">
+        <v>25</v>
+      </c>
+      <c r="P53" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V53" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X53" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>4042.43</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>4271.06</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI53"/>
+  <dimension ref="A1:BI54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -11165,6 +11165,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>20260913</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>25</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>24</v>
+      </c>
+      <c r="J54" t="n">
+        <v>25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>24</v>
+      </c>
+      <c r="L54" t="n">
+        <v>25</v>
+      </c>
+      <c r="M54" t="n">
+        <v>25</v>
+      </c>
+      <c r="N54" t="n">
+        <v>24</v>
+      </c>
+      <c r="O54" t="n">
+        <v>25</v>
+      </c>
+      <c r="P54" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V54" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W54" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>4042.42</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>4271.06</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
